--- a/docs/sample-trial-grouped.xlsx
+++ b/docs/sample-trial-grouped.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Participants" sheetId="1" r:id="Rce2715eaae154781"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" r:id="R39aebecd39844fb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Participants" sheetId="1" r:id="R674fedd5c7574719"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="2" r:id="R9980482445b24e59"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -372,22 +372,22 @@
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
       <x:c r="A4" s="12" t="str">
-        <x:v>C-Wags reg number</x:v>
+        <x:v>Reg Number</x:v>
       </x:c>
       <x:c r="B4" s="12" t="str">
         <x:v>Handler</x:v>
       </x:c>
       <x:c r="C4" s="12" t="str">
-        <x:v>Dog call name</x:v>
+        <x:v>Dog Call Name</x:v>
       </x:c>
       <x:c r="D4" s="12" t="str">
-        <x:v>Reg or FEO</x:v>
+        <x:v>Reg/FEO</x:v>
       </x:c>
       <x:c r="E4" s="12" t="str">
         <x:v>Division</x:v>
       </x:c>
       <x:c r="F4" s="13" t="str">
-        <x:v>Jump height</x:v>
+        <x:v>Jump Height</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="25" customHeight="1">
@@ -510,22 +510,22 @@
     </x:row>
     <x:row r="13" ht="30" customHeight="1">
       <x:c r="A13" s="12" t="str">
-        <x:v>C-Wags reg number</x:v>
+        <x:v>Reg Number</x:v>
       </x:c>
       <x:c r="B13" s="12" t="str">
         <x:v>Handler</x:v>
       </x:c>
       <x:c r="C13" s="12" t="str">
-        <x:v>Dog call name</x:v>
+        <x:v>Dog Call Name</x:v>
       </x:c>
       <x:c r="D13" s="12" t="str">
-        <x:v>Reg or FEO</x:v>
+        <x:v>Reg/FEO</x:v>
       </x:c>
       <x:c r="E13" s="12" t="str">
         <x:v>Division</x:v>
       </x:c>
       <x:c r="F13" s="13" t="str">
-        <x:v>Jump height</x:v>
+        <x:v>Jump Height</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="25" customHeight="1">
@@ -648,22 +648,22 @@
     </x:row>
     <x:row r="22" ht="30" customHeight="1">
       <x:c r="A22" s="12" t="str">
-        <x:v>C-Wags reg number</x:v>
+        <x:v>Reg Number</x:v>
       </x:c>
       <x:c r="B22" s="12" t="str">
         <x:v>Handler</x:v>
       </x:c>
       <x:c r="C22" s="12" t="str">
-        <x:v>Dog call name</x:v>
+        <x:v>Dog Call Name</x:v>
       </x:c>
       <x:c r="D22" s="12" t="str">
-        <x:v>Reg or FEO</x:v>
+        <x:v>Reg/FEO</x:v>
       </x:c>
       <x:c r="E22" s="12" t="str">
         <x:v>Division</x:v>
       </x:c>
       <x:c r="F22" s="13" t="str">
-        <x:v>Jump height</x:v>
+        <x:v>Jump Height</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="25" customHeight="1">
@@ -786,22 +786,22 @@
     </x:row>
     <x:row r="31" ht="30" customHeight="1">
       <x:c r="A31" s="12" t="str">
-        <x:v>C-Wags reg number</x:v>
+        <x:v>Reg Number</x:v>
       </x:c>
       <x:c r="B31" s="12" t="str">
         <x:v>Handler</x:v>
       </x:c>
       <x:c r="C31" s="12" t="str">
-        <x:v>Dog call name</x:v>
+        <x:v>Dog Call Name</x:v>
       </x:c>
       <x:c r="D31" s="12" t="str">
-        <x:v>Reg or FEO</x:v>
+        <x:v>Reg/FEO</x:v>
       </x:c>
       <x:c r="E31" s="12" t="str">
         <x:v>Division</x:v>
       </x:c>
       <x:c r="F31" s="13" t="str">
-        <x:v>Jump height</x:v>
+        <x:v>Jump Height</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="25" customHeight="1">
@@ -924,22 +924,22 @@
     </x:row>
     <x:row r="40" ht="30" customHeight="1">
       <x:c r="A40" s="12" t="str">
-        <x:v>C-Wags reg number</x:v>
+        <x:v>Reg Number</x:v>
       </x:c>
       <x:c r="B40" s="12" t="str">
         <x:v>Handler</x:v>
       </x:c>
       <x:c r="C40" s="12" t="str">
-        <x:v>Dog call name</x:v>
+        <x:v>Dog Call Name</x:v>
       </x:c>
       <x:c r="D40" s="12" t="str">
-        <x:v>Reg or FEO</x:v>
+        <x:v>Reg/FEO</x:v>
       </x:c>
       <x:c r="E40" s="12" t="str">
         <x:v>Division</x:v>
       </x:c>
       <x:c r="F40" s="13" t="str">
-        <x:v>Jump height</x:v>
+        <x:v>Jump Height</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="25" customHeight="1">
@@ -1046,22 +1046,22 @@
     </x:row>
     <x:row r="49" ht="30" customHeight="1">
       <x:c r="A49" s="12" t="str">
-        <x:v>C-Wags reg number</x:v>
+        <x:v>Reg Number</x:v>
       </x:c>
       <x:c r="B49" s="12" t="str">
         <x:v>Handler</x:v>
       </x:c>
       <x:c r="C49" s="12" t="str">
-        <x:v>Dog call name</x:v>
+        <x:v>Dog Call Name</x:v>
       </x:c>
       <x:c r="D49" s="12" t="str">
-        <x:v>Reg or FEO</x:v>
+        <x:v>Reg/FEO</x:v>
       </x:c>
       <x:c r="E49" s="12" t="str">
         <x:v>Division</x:v>
       </x:c>
       <x:c r="F49" s="13" t="str">
-        <x:v>Jump height</x:v>
+        <x:v>Jump Height</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="25" customHeight="1">
@@ -1226,7 +1226,7 @@
         <x:v>Class blocks</x:v>
       </x:c>
       <x:c r="B6" s="22" t="str">
-        <x:v>Each class starts with its name, then judge, then Round 1 or Round 2, followed by the six participant headings.</x:v>
+        <x:v>Enter Class, then Judge, then Round on separate rows. Add six headers: Reg Number, Handler, Dog Call Name, Reg/FEO, Division, Jump Height. Fill all participants; repeat for every round.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="42" customHeight="1">
